--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/147.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/147.xlsx
@@ -426,13 +426,13 @@
         <v>-12.08212978086099</v>
       </c>
       <c r="E2">
-        <v>-11.4549540704932</v>
+        <v>-12.72804209110422</v>
       </c>
       <c r="F2">
-        <v>2.360286145999388</v>
+        <v>1.13025167325643</v>
       </c>
       <c r="G2">
-        <v>-10.46838558664478</v>
+        <v>-7.249111676394962</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.91116612741146</v>
       </c>
       <c r="E3">
-        <v>-11.29437846104135</v>
+        <v>-12.55197500341076</v>
       </c>
       <c r="F3">
-        <v>2.484151923739998</v>
+        <v>1.221271026741234</v>
       </c>
       <c r="G3">
-        <v>-10.04434192329468</v>
+        <v>-6.304638270135456</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.67771137570424</v>
       </c>
       <c r="E4">
-        <v>-13.18607069564028</v>
+        <v>-12.93164912309261</v>
       </c>
       <c r="F4">
-        <v>2.304411107945756</v>
+        <v>1.266647336331785</v>
       </c>
       <c r="G4">
-        <v>-9.194532810536643</v>
+        <v>-6.189044942619324</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.41786709556964</v>
       </c>
       <c r="E5">
-        <v>-13.88857393160106</v>
+        <v>-13.7487560723507</v>
       </c>
       <c r="F5">
-        <v>2.547629717816524</v>
+        <v>1.515591621690704</v>
       </c>
       <c r="G5">
-        <v>-9.202862391154589</v>
+        <v>-6.387302276123876</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.12785708887223</v>
       </c>
       <c r="E6">
-        <v>-12.68324555375461</v>
+        <v>-14.32125133421037</v>
       </c>
       <c r="F6">
-        <v>3.142086046883116</v>
+        <v>2.01497125373358</v>
       </c>
       <c r="G6">
-        <v>-9.119500010988046</v>
+        <v>-5.696152028284682</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.82973640492675</v>
       </c>
       <c r="E7">
-        <v>-15.08449528579676</v>
+        <v>-14.65529412106633</v>
       </c>
       <c r="F7">
-        <v>2.196357207189783</v>
+        <v>1.797629184791463</v>
       </c>
       <c r="G7">
-        <v>-8.481659862327092</v>
+        <v>-5.483146598584931</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.52751989995984</v>
       </c>
       <c r="E8">
-        <v>-16.40835216164248</v>
+        <v>-15.32643645831332</v>
       </c>
       <c r="F8">
-        <v>2.355088968914224</v>
+        <v>1.873708103799375</v>
       </c>
       <c r="G8">
-        <v>-8.689750565334071</v>
+        <v>-5.125545079706371</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.23016767504556</v>
       </c>
       <c r="E9">
-        <v>-15.52820361768482</v>
+        <v>-15.53774354409795</v>
       </c>
       <c r="F9">
-        <v>3.060869593243042</v>
+        <v>2.03406843583772</v>
       </c>
       <c r="G9">
-        <v>-8.735787130081468</v>
+        <v>-5.293857172750854</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.946939561051138</v>
       </c>
       <c r="E10">
-        <v>-16.09792038116817</v>
+        <v>-15.92312002292879</v>
       </c>
       <c r="F10">
-        <v>2.944305045790707</v>
+        <v>2.54237621174797</v>
       </c>
       <c r="G10">
-        <v>-8.417342863952721</v>
+        <v>-5.302336871182789</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.676785046155992</v>
       </c>
       <c r="E11">
-        <v>-17.36906885209049</v>
+        <v>-17.00312524904853</v>
       </c>
       <c r="F11">
-        <v>3.341078121118419</v>
+        <v>2.706026819110234</v>
       </c>
       <c r="G11">
-        <v>-6.928922127507056</v>
+        <v>-4.741564597479202</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.438755187026477</v>
       </c>
       <c r="E12">
-        <v>-17.15271976775752</v>
+        <v>-17.67374012845726</v>
       </c>
       <c r="F12">
-        <v>4.378419425356962</v>
+        <v>2.695466791459346</v>
       </c>
       <c r="G12">
-        <v>-7.932912678210172</v>
+        <v>-4.649862193716348</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.226646703097201</v>
       </c>
       <c r="E13">
-        <v>-18.34591246211282</v>
+        <v>-17.9999665715999</v>
       </c>
       <c r="F13">
-        <v>3.759229702377582</v>
+        <v>3.131345435138418</v>
       </c>
       <c r="G13">
-        <v>-7.346972826648253</v>
+        <v>-4.525588140434765</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.069118738750902</v>
       </c>
       <c r="E14">
-        <v>-18.70503233894809</v>
+        <v>-19.16067284697238</v>
       </c>
       <c r="F14">
-        <v>4.376522464004551</v>
+        <v>3.336290157530238</v>
       </c>
       <c r="G14">
-        <v>-7.935710091039549</v>
+        <v>-4.432750062774776</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.958237766931521</v>
       </c>
       <c r="E15">
-        <v>-20.5214808439751</v>
+        <v>-20.35971326287303</v>
       </c>
       <c r="F15">
-        <v>4.713633205513032</v>
+        <v>3.905665178374867</v>
       </c>
       <c r="G15">
-        <v>-6.156718703092159</v>
+        <v>-4.329826678759318</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.915225390570848</v>
       </c>
       <c r="E16">
-        <v>-20.47523898908446</v>
+        <v>-20.15653816486242</v>
       </c>
       <c r="F16">
-        <v>4.765267002464331</v>
+        <v>4.276849984630103</v>
       </c>
       <c r="G16">
-        <v>-6.419406602360795</v>
+        <v>-4.301092823789524</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.926662943339958</v>
       </c>
       <c r="E17">
-        <v>-20.60901392585719</v>
+        <v>-21.30605153571449</v>
       </c>
       <c r="F17">
-        <v>5.29744169998404</v>
+        <v>4.49554394917359</v>
       </c>
       <c r="G17">
-        <v>-6.273719221942901</v>
+        <v>-4.444046754620524</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.994248559369572</v>
       </c>
       <c r="E18">
-        <v>-21.14057513689934</v>
+        <v>-21.92625888927378</v>
       </c>
       <c r="F18">
-        <v>5.535860749122988</v>
+        <v>4.963223617446134</v>
       </c>
       <c r="G18">
-        <v>-5.357619387899613</v>
+        <v>-4.121998355583744</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.09963365076019</v>
       </c>
       <c r="E19">
-        <v>-22.95530005922655</v>
+        <v>-22.51209011269747</v>
       </c>
       <c r="F19">
-        <v>5.462598279284594</v>
+        <v>5.343373015734467</v>
       </c>
       <c r="G19">
-        <v>-5.160521224993516</v>
+        <v>-4.054359184717181</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.22727994953134</v>
       </c>
       <c r="E20">
-        <v>-23.09995640967033</v>
+        <v>-22.79768984266063</v>
       </c>
       <c r="F20">
-        <v>6.189798827915002</v>
+        <v>5.685697501676168</v>
       </c>
       <c r="G20">
-        <v>-6.160922001883852</v>
+        <v>-3.529320172232162</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.362368161856532</v>
       </c>
       <c r="E21">
-        <v>-23.46686355773966</v>
+        <v>-24.45430200985162</v>
       </c>
       <c r="F21">
-        <v>6.503214948233806</v>
+        <v>6.099501810805439</v>
       </c>
       <c r="G21">
-        <v>-4.819918264147694</v>
+        <v>-3.201146966384631</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.483651946908116</v>
       </c>
       <c r="E22">
-        <v>-24.14235430724375</v>
+        <v>-23.97448981191683</v>
       </c>
       <c r="F22">
-        <v>7.088065528897535</v>
+        <v>6.266187556331561</v>
       </c>
       <c r="G22">
-        <v>-5.211075683255833</v>
+        <v>-3.437779634633956</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.588861237222318</v>
       </c>
       <c r="E23">
-        <v>-24.87097293601504</v>
+        <v>-24.35740758964337</v>
       </c>
       <c r="F23">
-        <v>7.30410209081284</v>
+        <v>6.526226994683576</v>
       </c>
       <c r="G23">
-        <v>-5.345808379369417</v>
+        <v>-2.993979161590609</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.657700609935016</v>
       </c>
       <c r="E24">
-        <v>-24.91409572920074</v>
+        <v>-24.96661308640319</v>
       </c>
       <c r="F24">
-        <v>7.510529590855672</v>
+        <v>6.681844094973491</v>
       </c>
       <c r="G24">
-        <v>-5.288118756139586</v>
+        <v>-2.892643110286547</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.700313309375394</v>
       </c>
       <c r="E25">
-        <v>-28.04323520142667</v>
+        <v>-24.8108302828202</v>
       </c>
       <c r="F25">
-        <v>7.557953624665943</v>
+        <v>6.812898445035596</v>
       </c>
       <c r="G25">
-        <v>-5.094378010777661</v>
+        <v>-3.101708926398308</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.701525991958603</v>
       </c>
       <c r="E26">
-        <v>-25.34415660867541</v>
+        <v>-24.92565826952906</v>
       </c>
       <c r="F26">
-        <v>7.638326800289969</v>
+        <v>6.607597524660571</v>
       </c>
       <c r="G26">
-        <v>-5.127845145691142</v>
+        <v>-3.36586406412715</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.675966088439797</v>
       </c>
       <c r="E27">
-        <v>-25.83672747180007</v>
+        <v>-25.44948204787306</v>
       </c>
       <c r="F27">
-        <v>6.936003781500435</v>
+        <v>6.640728907302941</v>
       </c>
       <c r="G27">
-        <v>-5.502408672178166</v>
+        <v>-3.233008493374577</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.615264067298344</v>
       </c>
       <c r="E28">
-        <v>-25.94123057515541</v>
+        <v>-25.84466841185314</v>
       </c>
       <c r="F28">
-        <v>7.512169758313215</v>
+        <v>6.44384419974036</v>
       </c>
       <c r="G28">
-        <v>-5.092918604551229</v>
+        <v>-3.100727286432049</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.529569037709544</v>
       </c>
       <c r="E29">
-        <v>-25.01699569298469</v>
+        <v>-25.36817878297822</v>
       </c>
       <c r="F29">
-        <v>7.595303054123367</v>
+        <v>6.068386674421483</v>
       </c>
       <c r="G29">
-        <v>-4.9030861438422</v>
+        <v>-3.438403602591233</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.415100274164054</v>
       </c>
       <c r="E30">
-        <v>-25.27740204305144</v>
+        <v>-25.21240013260655</v>
       </c>
       <c r="F30">
-        <v>6.760891882753037</v>
+        <v>6.312145379838878</v>
       </c>
       <c r="G30">
-        <v>-4.856113627158889</v>
+        <v>-3.018332187136514</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.27323498350956</v>
       </c>
       <c r="E31">
-        <v>-24.15968565810225</v>
+        <v>-24.78615605433939</v>
       </c>
       <c r="F31">
-        <v>6.531969237519783</v>
+        <v>5.725525406402769</v>
       </c>
       <c r="G31">
-        <v>-4.360946754285388</v>
+        <v>-2.840141036559259</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.103823197141608</v>
       </c>
       <c r="E32">
-        <v>-24.51434913918599</v>
+        <v>-24.48693379123079</v>
       </c>
       <c r="F32">
-        <v>6.241956153064869</v>
+        <v>5.795930008701504</v>
       </c>
       <c r="G32">
-        <v>-4.603952250081622</v>
+        <v>-2.662477256389408</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.901373414521483</v>
       </c>
       <c r="E33">
-        <v>-24.0683606942806</v>
+        <v>-24.16906360927372</v>
       </c>
       <c r="F33">
-        <v>5.793966777956869</v>
+        <v>5.33280139093994</v>
       </c>
       <c r="G33">
-        <v>-4.691613221217432</v>
+        <v>-2.848693835839746</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.673565704213285</v>
       </c>
       <c r="E34">
-        <v>-23.76835347423161</v>
+        <v>-24.44462918067609</v>
       </c>
       <c r="F34">
-        <v>6.871722471043194</v>
+        <v>5.466400485663444</v>
       </c>
       <c r="G34">
-        <v>-5.047875428120751</v>
+        <v>-2.404023984847558</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.412462549693005</v>
       </c>
       <c r="E35">
-        <v>-23.20835107203703</v>
+        <v>-23.96268638533166</v>
       </c>
       <c r="F35">
-        <v>5.883902626878811</v>
+        <v>5.054847679134983</v>
       </c>
       <c r="G35">
-        <v>-3.9461542643939</v>
+        <v>-2.757424815679017</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.135086071642315</v>
       </c>
       <c r="E36">
-        <v>-24.98695136226088</v>
+        <v>-23.25602163162341</v>
       </c>
       <c r="F36">
-        <v>6.231300034795257</v>
+        <v>5.211319654584586</v>
       </c>
       <c r="G36">
-        <v>-4.303311956691971</v>
+        <v>-2.148831533300007</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.836086841512</v>
       </c>
       <c r="E37">
-        <v>-22.22300999164411</v>
+        <v>-22.47994841025463</v>
       </c>
       <c r="F37">
-        <v>6.71857059214401</v>
+        <v>5.213024434699548</v>
       </c>
       <c r="G37">
-        <v>-4.040211559777938</v>
+        <v>-1.470223302476522</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.536058765387849</v>
       </c>
       <c r="E38">
-        <v>-22.68051944476457</v>
+        <v>-22.31506592065893</v>
       </c>
       <c r="F38">
-        <v>6.099143956087429</v>
+        <v>4.944770905181373</v>
       </c>
       <c r="G38">
-        <v>-3.621249710774443</v>
+        <v>-1.152500907227217</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.234603482622489</v>
       </c>
       <c r="E39">
-        <v>-23.54344462135817</v>
+        <v>-22.40830136169001</v>
       </c>
       <c r="F39">
-        <v>6.451450269232865</v>
+        <v>4.905103703730916</v>
       </c>
       <c r="G39">
-        <v>-3.53109808929871</v>
+        <v>-1.18275943703822</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.948682687369723</v>
       </c>
       <c r="E40">
-        <v>-23.14813366103834</v>
+        <v>-21.71529236681779</v>
       </c>
       <c r="F40">
-        <v>6.007509953989748</v>
+        <v>4.872533954187644</v>
       </c>
       <c r="G40">
-        <v>-3.548297674664964</v>
+        <v>-0.7635965607012091</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.68103939636052</v>
       </c>
       <c r="E41">
-        <v>-22.66079169097164</v>
+        <v>-21.87552325972968</v>
       </c>
       <c r="F41">
-        <v>6.082336381484628</v>
+        <v>4.987600813375718</v>
       </c>
       <c r="G41">
-        <v>-2.409652750185998</v>
+        <v>-0.7836235824596391</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.439534688554427</v>
       </c>
       <c r="E42">
-        <v>-21.44421641685756</v>
+        <v>-20.71786544146962</v>
       </c>
       <c r="F42">
-        <v>5.738025470511013</v>
+        <v>4.882729500181301</v>
       </c>
       <c r="G42">
-        <v>-2.840177586983534</v>
+        <v>-0.06547562480374317</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.228034761629741</v>
       </c>
       <c r="E43">
-        <v>-22.28767133876036</v>
+        <v>-20.84773635959701</v>
       </c>
       <c r="F43">
-        <v>5.745812124097328</v>
+        <v>4.859656154543724</v>
       </c>
       <c r="G43">
-        <v>-3.415327231150382</v>
+        <v>0.1527173543985497</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.043869607726572</v>
       </c>
       <c r="E44">
-        <v>-19.7900504911369</v>
+        <v>-20.43969580656658</v>
       </c>
       <c r="F44">
-        <v>5.989345513581161</v>
+        <v>4.857865224218871</v>
       </c>
       <c r="G44">
-        <v>-2.50125594565439</v>
+        <v>-0.1117615156595906</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.889447705039574</v>
       </c>
       <c r="E45">
-        <v>-21.20142798923073</v>
+        <v>-19.83577734782326</v>
       </c>
       <c r="F45">
-        <v>5.474226900885093</v>
+        <v>4.769002939450957</v>
       </c>
       <c r="G45">
-        <v>-2.213943503402373</v>
+        <v>0.3047122937485741</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.749673606405653</v>
       </c>
       <c r="E46">
-        <v>-20.3313219102565</v>
+        <v>-19.98457029674657</v>
       </c>
       <c r="F46">
-        <v>5.739234886919101</v>
+        <v>4.609838769942254</v>
       </c>
       <c r="G46">
-        <v>-2.99431072615368</v>
+        <v>0.6344728323075021</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.626097883396898</v>
       </c>
       <c r="E47">
-        <v>-20.12173425396035</v>
+        <v>-19.56376692531494</v>
       </c>
       <c r="F47">
-        <v>5.574083277822963</v>
+        <v>4.749009463816988</v>
       </c>
       <c r="G47">
-        <v>-1.087822320726977</v>
+        <v>0.6220639632659406</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.502237688832327</v>
       </c>
       <c r="E48">
-        <v>-19.26979847453225</v>
+        <v>-19.40596981423941</v>
       </c>
       <c r="F48">
-        <v>5.641951419134326</v>
+        <v>4.160088285735902</v>
       </c>
       <c r="G48">
-        <v>-2.600344145865503</v>
+        <v>0.6780409380440006</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.384197507594608</v>
       </c>
       <c r="E49">
-        <v>-18.75556446113728</v>
+        <v>-18.59381764609183</v>
       </c>
       <c r="F49">
-        <v>5.107079557351102</v>
+        <v>4.713383038557387</v>
       </c>
       <c r="G49">
-        <v>-1.433200333429945</v>
+        <v>1.256725530387216</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.263002421668386</v>
       </c>
       <c r="E50">
-        <v>-18.51025503423628</v>
+        <v>-18.40307726278776</v>
       </c>
       <c r="F50">
-        <v>5.287169944189326</v>
+        <v>4.160752636392947</v>
       </c>
       <c r="G50">
-        <v>-2.370572514401623</v>
+        <v>0.9076193744081384</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.146266744990068</v>
       </c>
       <c r="E51">
-        <v>-18.56061687476115</v>
+        <v>-18.22737981090221</v>
       </c>
       <c r="F51">
-        <v>5.807026818429406</v>
+        <v>3.968008109109558</v>
       </c>
       <c r="G51">
-        <v>-1.728726178165604</v>
+        <v>1.410581930630704</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.031758234205085</v>
       </c>
       <c r="E52">
-        <v>-18.00656187118373</v>
+        <v>-17.77711771154357</v>
       </c>
       <c r="F52">
-        <v>5.269103251134268</v>
+        <v>4.006325071693452</v>
       </c>
       <c r="G52">
-        <v>-2.061739704485059</v>
+        <v>1.052735001760579</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.923383586892608</v>
       </c>
       <c r="E53">
-        <v>-17.79771763971472</v>
+        <v>-17.7407895720853</v>
       </c>
       <c r="F53">
-        <v>5.219069860005178</v>
+        <v>4.033069741660237</v>
       </c>
       <c r="G53">
-        <v>-1.856459468030413</v>
+        <v>1.445307444437102</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.822103387201311</v>
       </c>
       <c r="E54">
-        <v>-16.8863618658623</v>
+        <v>-16.9976513165224</v>
       </c>
       <c r="F54">
-        <v>5.002859340935285</v>
+        <v>4.018275099846238</v>
       </c>
       <c r="G54">
-        <v>-1.931742899059755</v>
+        <v>1.407801487641168</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.727617003594102</v>
       </c>
       <c r="E55">
-        <v>-17.50099145661235</v>
+        <v>-17.3478085633187</v>
       </c>
       <c r="F55">
-        <v>5.153087082902587</v>
+        <v>3.856518140366773</v>
       </c>
       <c r="G55">
-        <v>-1.42681184141549</v>
+        <v>1.046351731235307</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.646859013680129</v>
       </c>
       <c r="E56">
-        <v>-17.03896330957047</v>
+        <v>-17.02507497090025</v>
       </c>
       <c r="F56">
-        <v>4.860027263140178</v>
+        <v>4.084199891230633</v>
       </c>
       <c r="G56">
-        <v>-1.290141972815301</v>
+        <v>1.513346059226105</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.577139843868715</v>
       </c>
       <c r="E57">
-        <v>-16.87178409411215</v>
+        <v>-17.08451573138119</v>
       </c>
       <c r="F57">
-        <v>5.1974461573225</v>
+        <v>4.019771131375694</v>
       </c>
       <c r="G57">
-        <v>-1.938943332642046</v>
+        <v>0.7422260938165207</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.528687144272348</v>
       </c>
       <c r="E58">
-        <v>-15.79376410300568</v>
+        <v>-16.9994081249128</v>
       </c>
       <c r="F58">
-        <v>4.885058869317973</v>
+        <v>3.993833291259235</v>
       </c>
       <c r="G58">
-        <v>-2.103801410592486</v>
+        <v>0.786251079856464</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.495554097776368</v>
       </c>
       <c r="E59">
-        <v>-17.11171095913617</v>
+        <v>-16.65656468325953</v>
       </c>
       <c r="F59">
-        <v>4.525491087519597</v>
+        <v>3.90078940784199</v>
       </c>
       <c r="G59">
-        <v>-2.504777840107802</v>
+        <v>0.3410146972880043</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.487094784021855</v>
       </c>
       <c r="E60">
-        <v>-17.60558593061683</v>
+        <v>-16.96113212934318</v>
       </c>
       <c r="F60">
-        <v>4.866781770942604</v>
+        <v>4.294963066259717</v>
       </c>
       <c r="G60">
-        <v>-1.827357498073273</v>
+        <v>0.9373165941320521</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.495118098477819</v>
       </c>
       <c r="E61">
-        <v>-15.2361373376889</v>
+        <v>-16.46225669142743</v>
       </c>
       <c r="F61">
-        <v>4.632020792254419</v>
+        <v>4.110835216700249</v>
       </c>
       <c r="G61">
-        <v>-1.926889524864876</v>
+        <v>0.5203284680394381</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.522411201404307</v>
       </c>
       <c r="E62">
-        <v>-16.0892609355559</v>
+        <v>-16.85388790651346</v>
       </c>
       <c r="F62">
-        <v>5.006479306485519</v>
+        <v>3.889048128274709</v>
       </c>
       <c r="G62">
-        <v>-3.002894854369261</v>
+        <v>0.06939805151776028</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.560152982192196</v>
       </c>
       <c r="E63">
-        <v>-15.74105569808228</v>
+        <v>-16.59469844736489</v>
       </c>
       <c r="F63">
-        <v>5.150189453727594</v>
+        <v>4.047183465469135</v>
       </c>
       <c r="G63">
-        <v>-2.534140884524053</v>
+        <v>-0.4697885859065022</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.604995275110897</v>
       </c>
       <c r="E64">
-        <v>-14.9097489193046</v>
+        <v>-15.81860445993948</v>
       </c>
       <c r="F64">
-        <v>5.048275412161171</v>
+        <v>4.016283704609908</v>
       </c>
       <c r="G64">
-        <v>-2.965931932448279</v>
+        <v>-0.3839003103480573</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.651494111166365</v>
       </c>
       <c r="E65">
-        <v>-16.05418706591773</v>
+        <v>-15.82404101356368</v>
       </c>
       <c r="F65">
-        <v>4.715999022815428</v>
+        <v>3.852185778850131</v>
       </c>
       <c r="G65">
-        <v>-3.353891189432304</v>
+        <v>-0.3159661253426985</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.693946731880058</v>
       </c>
       <c r="E66">
-        <v>-16.83399402426753</v>
+        <v>-16.35144070685836</v>
       </c>
       <c r="F66">
-        <v>4.333164057407219</v>
+        <v>4.003072901270061</v>
       </c>
       <c r="G66">
-        <v>-2.836196201482087</v>
+        <v>-0.4123026007547787</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.731210249839687</v>
       </c>
       <c r="E67">
-        <v>-17.07179029188192</v>
+        <v>-15.85589614442511</v>
       </c>
       <c r="F67">
-        <v>4.506239829078537</v>
+        <v>3.584411045690774</v>
       </c>
       <c r="G67">
-        <v>-2.185911938727589</v>
+        <v>-0.5080072759758095</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.754913625542882</v>
       </c>
       <c r="E68">
-        <v>-15.24414888233449</v>
+        <v>-15.02062304883222</v>
       </c>
       <c r="F68">
-        <v>4.411492822281135</v>
+        <v>3.825943099529443</v>
       </c>
       <c r="G68">
-        <v>-2.684498887015449</v>
+        <v>-0.8643190870263596</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.767994893804786</v>
       </c>
       <c r="E69">
-        <v>-14.82834597733796</v>
+        <v>-15.7636076355761</v>
       </c>
       <c r="F69">
-        <v>4.103045249644322</v>
+        <v>3.719915385440717</v>
       </c>
       <c r="G69">
-        <v>-2.593125437071075</v>
+        <v>-0.5835204525291703</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.76164458705348</v>
       </c>
       <c r="E70">
-        <v>-14.90393857666116</v>
+        <v>-15.58236979978323</v>
       </c>
       <c r="F70">
-        <v>4.007832700366547</v>
+        <v>3.845497540439928</v>
       </c>
       <c r="G70">
-        <v>-2.76585229921913</v>
+        <v>-0.6958581815401838</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.742231132827635</v>
       </c>
       <c r="E71">
-        <v>-14.46804243527511</v>
+        <v>-15.88577434669593</v>
       </c>
       <c r="F71">
-        <v>4.499427335557914</v>
+        <v>3.735195450552757</v>
       </c>
       <c r="G71">
-        <v>-2.596433250468016</v>
+        <v>-0.7363116689794842</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.70414539798879</v>
       </c>
       <c r="E72">
-        <v>-14.64159683011704</v>
+        <v>-15.69718948006944</v>
       </c>
       <c r="F72">
-        <v>4.41973507793899</v>
+        <v>3.606644426781913</v>
       </c>
       <c r="G72">
-        <v>-3.003179425529692</v>
+        <v>-0.3880905554167941</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.65552411887581</v>
       </c>
       <c r="E73">
-        <v>-15.76276038046583</v>
+        <v>-16.15543820480572</v>
       </c>
       <c r="F73">
-        <v>4.13216402058753</v>
+        <v>3.59768977515765</v>
       </c>
       <c r="G73">
-        <v>-1.956928752130225</v>
+        <v>-0.2126328544264346</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.595461949960737</v>
       </c>
       <c r="E74">
-        <v>-16.83549748676712</v>
+        <v>-15.90603371153844</v>
       </c>
       <c r="F74">
-        <v>4.272317158201984</v>
+        <v>3.460744076126836</v>
       </c>
       <c r="G74">
-        <v>-2.453649018035439</v>
+        <v>-0.3085255032580256</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.52949376481693</v>
       </c>
       <c r="E75">
-        <v>-15.57935872157273</v>
+        <v>-16.64447468509296</v>
       </c>
       <c r="F75">
-        <v>4.048755706799648</v>
+        <v>3.687493085295145</v>
       </c>
       <c r="G75">
-        <v>-2.108062145765182</v>
+        <v>-0.437681648924991</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.459784945985589</v>
       </c>
       <c r="E76">
-        <v>-14.95741532567965</v>
+        <v>-16.19757253369611</v>
       </c>
       <c r="F76">
-        <v>3.941576562021031</v>
+        <v>3.43744044435128</v>
       </c>
       <c r="G76">
-        <v>-2.811848397425364</v>
+        <v>-0.3124337879109222</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.388136457939554</v>
       </c>
       <c r="E77">
-        <v>-15.69945298024147</v>
+        <v>-16.63679124414202</v>
       </c>
       <c r="F77">
-        <v>3.883670367095735</v>
+        <v>3.155083131433041</v>
       </c>
       <c r="G77">
-        <v>-1.688891437194398</v>
+        <v>-0.07096602067885441</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.319546506070482</v>
       </c>
       <c r="E78">
-        <v>-17.06781982185538</v>
+        <v>-17.28595894026935</v>
       </c>
       <c r="F78">
-        <v>3.779256312707663</v>
+        <v>2.831918783518092</v>
       </c>
       <c r="G78">
-        <v>-1.58092931611809</v>
+        <v>0.2223511341327233</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.251639004516296</v>
       </c>
       <c r="E79">
-        <v>-16.92612886429753</v>
+        <v>-17.3241227991332</v>
       </c>
       <c r="F79">
-        <v>3.46596776096889</v>
+        <v>2.866945470778067</v>
       </c>
       <c r="G79">
-        <v>-1.573788929661395</v>
+        <v>0.8016361977318947</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.191520484493084</v>
       </c>
       <c r="E80">
-        <v>-16.10460705140115</v>
+        <v>-17.70753065579607</v>
       </c>
       <c r="F80">
-        <v>3.188961701472735</v>
+        <v>2.813282173689909</v>
       </c>
       <c r="G80">
-        <v>-0.7628028943455106</v>
+        <v>1.060018979169785</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.133664139918334</v>
       </c>
       <c r="E81">
-        <v>-18.98243362975604</v>
+        <v>-17.98371090247452</v>
       </c>
       <c r="F81">
-        <v>4.026515698769287</v>
+        <v>2.685912401835457</v>
       </c>
       <c r="G81">
-        <v>-0.7666432996390383</v>
+        <v>1.312303061242835</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.085854474589885</v>
       </c>
       <c r="E82">
-        <v>-18.69059577638299</v>
+        <v>-19.03989330843504</v>
       </c>
       <c r="F82">
-        <v>2.228383547716817</v>
+        <v>2.786873820888661</v>
       </c>
       <c r="G82">
-        <v>-0.7055701514191253</v>
+        <v>0.8930409766113619</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.041762983219796</v>
       </c>
       <c r="E83">
-        <v>-19.3492452539649</v>
+        <v>-19.43657067528074</v>
       </c>
       <c r="F83">
-        <v>2.519937395540937</v>
+        <v>2.525384739581746</v>
       </c>
       <c r="G83">
-        <v>-0.7799084929064849</v>
+        <v>1.702343081665978</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.006857649892185</v>
       </c>
       <c r="E84">
-        <v>-21.20055996806384</v>
+        <v>-20.88743690665104</v>
       </c>
       <c r="F84">
-        <v>3.299252194216267</v>
+        <v>2.200707792789286</v>
       </c>
       <c r="G84">
-        <v>-0.2707297538124786</v>
+        <v>1.212181006173641</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.976129900613929</v>
       </c>
       <c r="E85">
-        <v>-20.78933805515859</v>
+        <v>-21.38933172919995</v>
       </c>
       <c r="F85">
-        <v>3.080097657396824</v>
+        <v>2.394343643398087</v>
       </c>
       <c r="G85">
-        <v>-0.2742150978416148</v>
+        <v>1.600975701426823</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.950351423704958</v>
       </c>
       <c r="E86">
-        <v>-21.26412071417902</v>
+        <v>-22.0166742998153</v>
       </c>
       <c r="F86">
-        <v>3.037181598992587</v>
+        <v>1.968344109364802</v>
       </c>
       <c r="G86">
-        <v>0.09516871137663953</v>
+        <v>1.921170471803912</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.926040171807308</v>
       </c>
       <c r="E87">
-        <v>-22.26811801984307</v>
+        <v>-23.26607655624082</v>
       </c>
       <c r="F87">
-        <v>2.198794264088819</v>
+        <v>1.71862944232128</v>
       </c>
       <c r="G87">
-        <v>-0.6331898683751005</v>
+        <v>1.769982252532541</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.900879365022547</v>
       </c>
       <c r="E88">
-        <v>-23.94318290495027</v>
+        <v>-24.58560578588607</v>
       </c>
       <c r="F88">
-        <v>1.882825115434587</v>
+        <v>1.310499449901186</v>
       </c>
       <c r="G88">
-        <v>0.1584714354773634</v>
+        <v>1.84774328017885</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.876494962098783</v>
       </c>
       <c r="E89">
-        <v>-24.29978178251137</v>
+        <v>-25.40418297195315</v>
       </c>
       <c r="F89">
-        <v>2.141174684284891</v>
+        <v>1.443464015194146</v>
       </c>
       <c r="G89">
-        <v>-0.04337045035078698</v>
+        <v>2.100648719464586</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.850306853404658</v>
       </c>
       <c r="E90">
-        <v>-26.40476218469687</v>
+        <v>-26.35281797065724</v>
       </c>
       <c r="F90">
-        <v>1.995272676895008</v>
+        <v>1.045831094502327</v>
       </c>
       <c r="G90">
-        <v>0.3473796926011385</v>
+        <v>2.093946938099198</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.829876462632412</v>
       </c>
       <c r="E91">
-        <v>-28.53697519353927</v>
+        <v>-28.04892925415301</v>
       </c>
       <c r="F91">
-        <v>1.638567732840708</v>
+        <v>0.6452110809560132</v>
       </c>
       <c r="G91">
-        <v>-0.3046877087090891</v>
+        <v>2.282581067040906</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.812370010009548</v>
       </c>
       <c r="E92">
-        <v>-30.03631355428165</v>
+        <v>-29.3712182927236</v>
       </c>
       <c r="F92">
-        <v>1.757973580484645</v>
+        <v>0.4235291951906291</v>
       </c>
       <c r="G92">
-        <v>-0.8752685498414888</v>
+        <v>1.708705466234521</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.80832290687387</v>
       </c>
       <c r="E93">
-        <v>-30.97678333952112</v>
+        <v>-30.7767418394551</v>
       </c>
       <c r="F93">
-        <v>1.821409956191031</v>
+        <v>0.3816080060371545</v>
       </c>
       <c r="G93">
-        <v>-0.3776527985415232</v>
+        <v>1.817542186748852</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.814340149671609</v>
       </c>
       <c r="E94">
-        <v>-31.84878328285947</v>
+        <v>-33.57608726001037</v>
       </c>
       <c r="F94">
-        <v>0.7929620043889442</v>
+        <v>0.08452894763636221</v>
       </c>
       <c r="G94">
-        <v>-0.0192236736275802</v>
+        <v>2.07650455348597</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.838818989210768</v>
       </c>
       <c r="E95">
-        <v>-34.8881531689049</v>
+        <v>-35.15829464631705</v>
       </c>
       <c r="F95">
-        <v>0.5160346397960555</v>
+        <v>-0.2651224479831007</v>
       </c>
       <c r="G95">
-        <v>-1.315797759912171</v>
+        <v>1.700016908235296</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.878968998943541</v>
       </c>
       <c r="E96">
-        <v>-38.2307240945081</v>
+        <v>-37.15289307451692</v>
       </c>
       <c r="F96">
-        <v>0.1197759806254812</v>
+        <v>-0.4077681431125784</v>
       </c>
       <c r="G96">
-        <v>0.09748444182895701</v>
+        <v>1.831386965315526</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.935244518632499</v>
       </c>
       <c r="E97">
-        <v>-38.00028524075566</v>
+        <v>-39.38349773625016</v>
       </c>
       <c r="F97">
-        <v>-0.4468438902374366</v>
+        <v>-1.125277621497635</v>
       </c>
       <c r="G97">
-        <v>-1.715458374153567</v>
+        <v>1.281924437180641</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.004387634783475</v>
       </c>
       <c r="E98">
-        <v>-41.69599334228072</v>
+        <v>-41.16726254475644</v>
       </c>
       <c r="F98">
-        <v>0.2000969691031296</v>
+        <v>-1.211539660988161</v>
       </c>
       <c r="G98">
-        <v>-0.9051694076435093</v>
+        <v>0.9514198364132461</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.076998200641409</v>
       </c>
       <c r="E99">
-        <v>-43.75021527225983</v>
+        <v>-42.74071703819605</v>
       </c>
       <c r="F99">
-        <v>-0.05350688289653622</v>
+        <v>-1.278870191855108</v>
       </c>
       <c r="G99">
-        <v>-1.287463348864819</v>
+        <v>0.09111683577123171</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.151379026343038</v>
       </c>
       <c r="E100">
-        <v>-45.98789700609059</v>
+        <v>-44.94833575185203</v>
       </c>
       <c r="F100">
-        <v>-0.3924715106524827</v>
+        <v>-1.806572533767102</v>
       </c>
       <c r="G100">
-        <v>-1.448974452249451</v>
+        <v>0.5129165641452675</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.20774037414069</v>
       </c>
       <c r="E101">
-        <v>-47.16125500146133</v>
+        <v>-47.18234293196315</v>
       </c>
       <c r="F101">
-        <v>-0.9827164198432424</v>
+        <v>-2.048723378055662</v>
       </c>
       <c r="G101">
-        <v>-2.346723362561803</v>
+        <v>0.04258570456702684</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.253006957818537</v>
       </c>
       <c r="E102">
-        <v>-50.08730140160031</v>
+        <v>-49.04548599191521</v>
       </c>
       <c r="F102">
-        <v>-1.222603336019951</v>
+        <v>-2.335731973940621</v>
       </c>
       <c r="G102">
-        <v>-3.484914017481916</v>
+        <v>-0.4719137320036684</v>
       </c>
     </row>
   </sheetData>
